--- a/public/samples/rtm-format-sample.xlsx
+++ b/public/samples/rtm-format-sample.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="요구사항추적표(검토본)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="표에 없는 요구사항" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="지적 예상 목록" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="과업대비표(검토본)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="검사기준서·시험결과 대응" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항추적표(검토본)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세부 항목 판정" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="표에 없는 요구사항" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지적 예상 목록" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="과업대비표(검토본)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검사기준서·시험결과 대응" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -95,15 +96,11 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -484,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -521,7 +518,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>설계단계 (2단계 감리)</t>
+          <t>설계단계</t>
         </is>
       </c>
     </row>
@@ -533,7 +530,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -557,7 +554,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>RFP 원자 7 / 추적표 행 5 (견본 축약)</t>
+          <t>RFP 원자 7 / 표 행 5</t>
         </is>
       </c>
     </row>
@@ -589,81 +586,138 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>형식 요건 (FORM)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>추적성 (ROW·REF)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>설계 반영 (DSGN)</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>설계 반영 세부 항목 (DSGN)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>검사기준서 대응 (CRIT)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>시험결과 대응 (TEST · 종료 회차 견본)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>고정 문장</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>판정은 감리원의 점검 순서(형식 요건·추적성·설계 반영)를 문서만으로 먼저 수행한 예상입니다. 확정은 감리원이 합니다.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>보지 않은 것</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>사업관리·DB·시스템 구조·보안 영역, 시험 수행 여부.</t>
         </is>
@@ -680,16 +734,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -800,12 +854,12 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>화면정의서 §3.4 SCR-031 「이벤트 발생 시 사용자 화면에 알림 배너를 표시한다」— 도달 시간 기준 없음</t>
+          <t>화면정의서 §3.4 SCR-031 「이벤트 발생 시 사용자 화면에 알림 배너를 표시한다」 — 3초 이내 도달 ↔ 도달 시간 기준 없음</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>DSGN · 요구 「3초 이내 도달」 조건 미기술</t>
+          <t>DSGN · 3초 이내 도달 ↔ 도달 시간 기준 없음</t>
         </is>
       </c>
     </row>
@@ -898,12 +952,12 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>프로그램명세서·화면정의서·인터페이스정의서 3건에 PGM-118 없음</t>
+          <t>검색한 문서 3건에 PGM-118 없음</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>REF · 표가 가리킨 PGM-118 이 프로그램명세서에 없음</t>
+          <t>REF · 표가 가리킨 PGM-118 이(가) 산출물에 없음 · DSGN · 요구 「연계 이력(요청·응답·시각)을 관리」 미반영</t>
         </is>
       </c>
     </row>
@@ -918,11 +972,7 @@
           <t>관리자 권한 분리(조회/승인)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>UC-09</t>
-        </is>
-      </c>
+      <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
@@ -935,12 +985,12 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>설계 열(화면·프로그램) 비어 있음</t>
+          <t>유스케이스 ID·화면 ID·컴포넌트 ID·프로그램 ID 열 비어 있음</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>FORM · 설계단계 추적 항목 미기재</t>
+          <t>FORM · 설계단계 추적 항목 미기재(유스케이스 ID·화면 ID·컴포넌트 ID·프로그램 ID)</t>
         </is>
       </c>
     </row>
@@ -984,12 +1034,81 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>프로그램명세서 §7.2 PGM-140 「조회 결과의 개인정보 항목은 표시 정책에 따른다」— 마스킹 규칙 미확인</t>
+          <t>프로그램명세서 §7.2 PGM-140 「조회 결과의 개인정보 항목은 표시 정책에 따른다」 — 표가 갈림(covered/partial/covered/partial/partial) — 가장 무거운 표는 partial. 확인 필요</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>DSGN · 「표시 정책」이 별도 문서 참조. 정정(PM 확인 09-15): 별첨 3에 규칙 있음 → 적합 예상</t>
+          <t>DSGN · 표가 갈림(covered/partial/covered/partial/partial) — 가장 무거운 표는 partial. 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>표에 없음 — RFP 요구사항 중 대응 행이 없는 것(시트 ③과 같음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>SFR-007</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>SFR-007 수집 데이터의 원천·수집 시각·처리 이력을 메타데이터로 보존하여야 한다</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>부적합 예상</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>제안요청서</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>ROW · 추적표에 행 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>동시 사용자 200명 기준 화면 응답 3초 이내</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>제안요청서</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>ROW · 고유번호 없음, 이름 유사도로도 대응 안 됨 — 같은 항목인지 확인</t>
         </is>
       </c>
     </row>
@@ -999,6 +1118,277 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>요구사항의 세부 항목(RFP 표의 О 항목)마다 설계 절과 대조한 결과 전부. 시트 ② 의 판정은 이 중 가장 무거운 것</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>요구사항 ID</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>요구 세부 항목(원문 인용)</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>설계 문서 · 절</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>판정(예상)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>설계 인용</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>빠진 조건 · 비고</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>대응 방식</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>SFR-012 (1)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>SFR-012</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>「실시간 알림은 이벤트 발생 후 3초 이내 사용자에게 도달」</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>화면정의서 · §3.4 SCR-031</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>부적합 예상</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>「이벤트 발생 시 사용자 화면에 알림 배너를 표시한다」</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>3초 이내 도달 ↔ 도달 시간 기준 없음</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>표가 가리킨 ID 절</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>SFR-012 (2)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>SFR-012</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>「알림 이력은 30일간 보관」</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>화면정의서 · §3.4 SCR-031 표</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>적합 예상</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>「알림 이력은 30일간 보관하며 만료 이력은 배치가 삭제한다」</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>표가 가리킨 ID 절</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>SFR-015 (1)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>SFR-015</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>「키워드와 분류 체계(대·중·소)로 검색」</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>화면정의서 · §2.1 SCR-012</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>적합 예상</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>「키워드 및 분류 체계(대·중·소)로 데이터셋을 검색한다」</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>표가 가리킨 ID 절</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>SFR-020 (1)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>SFR-020</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>「연계 이력(요청·응답·시각)을 관리」</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>프로그램명세서</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>부적합 예상</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>요구를 다루는 절 없음</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>용어 겹침 절</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>SFR-033 (1)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>SFR-033</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>「개인정보 항목은 조회 화면에서 마스킹하여 표시」</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>프로그램명세서 · §7.2 PGM-140</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>「조회 결과의 개인정보 항목은 표시 정책에 따른다」</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>표가 갈림(covered/partial/covered/partial/partial) — 가장 무거운 표는 partial. 확인 필요</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>표가 가리킨 ID 절</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1056,12 +1446,12 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>「수집 데이터의 원천·수집 시각·처리 이력을 메타데이터로 보존하여야 한다」</t>
+          <t>「SFR-007 수집 데이터의 원천·수집 시각·처리 이력을 메타데이터로 보존하여야 한다」</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>제안요청서 §4.2 기능 요구사항 표</t>
+          <t>제안요청서</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1076,11 +1466,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>PER-002</t>
-        </is>
-      </c>
+      <c r="A5" s="6" t="inlineStr"/>
       <c r="B5" s="6" t="inlineStr">
         <is>
           <t>「동시 사용자 200명 기준 화면 응답 3초 이내」</t>
@@ -1088,7 +1474,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>제안요청서 §4.3 성능 요구사항</t>
+          <t>제안요청서</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -1098,7 +1484,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>ROW · 이름 유사도로만 대응 시도(0.61) — 표의 「응답 속도」 행과 같은 항목인지 확인</t>
+          <t>ROW · 고유번호 없음, 이름 유사도로도 대응 안 됨 — 같은 항목인지 확인</t>
         </is>
       </c>
     </row>
@@ -1107,13 +1493,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1174,22 +1560,22 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>SFR-007, PER-002</t>
+          <t>SFR-007</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>과업내용의 요구사항이 대비표에서 누락된 것이 확인되므로 보완할 필요가 있음. RFP SFR-007 등 2건이 추적표에 행으로 존재하지 않음. 예: 「수집 데이터의 원천·수집 시각·처리 이력을 메타데이터로 보존하여야 한다」</t>
+          <t>과업내용의 요구사항이 대비표에서 누락된 것이 확인되므로 보완할 필요가 있음. RFP SFR-007 1건이 추적표에 행으로 존재하지 않음. 예: 「SFR-007 수집 데이터의 원천·수집 시각·처리 이력을 메타데이터로 보존하여야 한다」</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>누락 요구사항을 추적표에 추가하고 설계 반영 여부를 확인</t>
+          <t>누락 요구사항을 추적표에 추가하고 설계 반영 여부를 확인.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>③ 1~2행</t>
+          <t>③</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1595,12 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>대비표가 가리킨 산출물 항목의 추적 가능 여부를 점검한 결과, 존재하지 않는 항목이 확인되므로 보완할 필요가 있음. PGM-118 이 프로그램명세서에 없음(검색 문서 3건)</t>
+          <t>대비표가 가리킨 산출물 항목의 추적 가능 여부를 점검한 결과, 존재하지 않는 항목이 확인되므로 보완할 필요가 있음. PGM-118 1건이 산출물에 없음(검색 문서 3건).</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>실제 산출물 ID 로 정정하거나 해당 프로그램명세를 작성</t>
+          <t>실제 산출물 ID 로 정정하거나 해당 산출물을 작성.</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -1234,22 +1620,22 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>SFR-012</t>
+          <t>SFR-012, SFR-020</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>설계 산출물이 요구사항의 내용을 적정하게 반영하고 있는지 점검한 결과, 핵심 조건이 반영되지 않은 항목이 확인되므로 보완할 필요가 있음. SFR-012: 요구 「3초 이내 도달」 ↔ 설계 「알림 배너를 표시한다」— 도달 시간 조건 미기술(1건)</t>
+          <t>설계 산출물이 요구사항의 내용을 적정하게 반영하고 있는지 점검한 결과, 핵심 조건이 반영되지 않은 항목이 확인되므로 보완할 필요가 있음. SFR-012: 요구 「실시간 알림은 이벤트 발생 후 3초 이내 사용자에게 도달」 ↔ 설계 「이벤트 발생 시 사용자 화면에 알림 배너를 표시한다」 — 3초 이내 도달 ↔ 도달 시간 기준 없음 미기술; SFR-020: 요구 「연계 이력(요청·응답·시각)을 관리」 ↔ 설계 「해당 절 없음」 — 요구를 다루는 절 없음 미기술 (2건)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>화면정의서 SCR-031 에 도달 시간 기준과 초과 시 처리를 명시하고 추적표 근거 갱신</t>
+          <t>설계서 해당 절에 조건(수치·기한·권한·예외)을 명시하고 추적표 근거 갱신.</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>② SFR-012</t>
+          <t>②-1 SFR-012 (1) · SFR-020 (1)</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1655,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>대비표의 요구사항ID별 관련 산출물 정보 작성 현황을 점검한 결과, 설계단계 추적 항목이 기재되지 않은 요구사항이 확인되므로 보완할 필요가 있음. SFR-031 의 화면 ID·프로그램 ID 열이 비어 있음(1건)</t>
+          <t>대비표의 요구사항ID별 관련 산출물 정보 작성 현황을 점검한 결과, 설계단계 추적 항목이 기재되지 않은 요구사항이 확인되므로 보완할 필요가 있음. 요구사항 1건(SFR-031)의 유스케이스 ID·화면 ID·컴포넌트 ID·프로그램 ID 열이 비어 있음.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>반영된 설계 산출물 ID 를 기재하고, 미반영이면 사유를 명시</t>
+          <t>해당 요구사항이 반영된 설계 산출물의 ID 를 기재하고, 미반영이면 사유(제외·이관·후속 단계)를 명시.</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1283,122 +1669,35 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>요구정의 회차(3단계)에서만 생성 — 견본</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>과업항목 ID</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>과업내용(계약문서)</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>요구사항정의서 ID</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>판정(예상)</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>근거</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>T-04</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>데이터 수집 메타데이터 보존</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>부적합 예상</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>요구사항정의서에 대응 ID 없음</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>ROW · 요구정의 회차 검사(3단계에서만)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>T-05</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>외부 API 연계</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-020</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>적합 예상</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>요구사항정의서 REQ-F-020 「외부 시스템 API 연계 및 이력 관리」</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr"/>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>E · 검사기준서 대응</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>CK-099</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>검사기준서의 검사항목이 요구사항과 대응되고 판정 가능한지 점검한 결과, 보완이 필요한 항목이 확인됨. 요구사항과 대응되지 않는 검사항목 1건 / 판정 기준이 없는 항목 0건.</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>요구사항ID 대응과 예상 결과·판정 기준을 기재.</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>검사기준서</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1411,7 +1710,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>요구정의 회차 — 과업대비표 원형 + 3열</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>과업항목 ID</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>과업내용</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>요구사항 ID</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>판정(예상)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>T-04</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>데이터 수집 메타데이터 보존</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>부적합 예상</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>요구사항정의서에 대응 ID 없음</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>ROW · 과업내용이 요구사항정의서에 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>T-05</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>외부 API 연계</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>REQ-F-020</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>적합 예상</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>요구사항정의서 REQ-F-020</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1427,7 +1847,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>종료 회차에서만 생성 — 견본</t>
+          <t>종료 회차 — 검사기준서 × 시험결과서</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1911,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>UT-031</t>
+          <t>CK-012</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -1529,7 +1949,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>UT-012</t>
+          <t>CK-015</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1579,6 +1999,44 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>CK-099</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>SFR-099</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>「정상 동작」</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CK-099</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>적합 예상</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
